--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="363">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -478,8 +478,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l’entrée. 
- - Attribué par le LPS avec un identifiant unique de type UUID affecté à l’attribut root (l’attribut extension est omis).</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>A unique identifier assigned to this particular recommendation record.</t>
@@ -713,19 +712,34 @@
     <t>cis</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:cis.id</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-vaccine-code-cis</t>
+  </si>
+  <si>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation</t>
+  </si>
+  <si>
+    <t>translation</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-medication-translation-document</t>
+  </si>
+  <si>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.id</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding.id</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:cis.extension</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.extension</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding.extension</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:cis.system</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.system</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding.system</t>
@@ -743,9 +757,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-bdpm</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -755,7 +766,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:cis.version</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.version</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding.version</t>
@@ -779,7 +790,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:cis.code</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.code</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding.code</t>
@@ -803,7 +814,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:cis.display</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.display</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding.display</t>
@@ -827,7 +838,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:cis.userSelected</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.userSelected</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding.userSelected</t>
@@ -856,39 +867,6 @@
   </si>
   <si>
     <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation</t>
-  </si>
-  <si>
-    <t>translation</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-medication-translation-document</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.id</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.extension</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.system</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.version</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.code</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.display</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.userSelected</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.text</t>
@@ -1484,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN56"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="75.48828125" customWidth="true" bestFit="true"/>
@@ -4097,13 +4075,11 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4150,12 +4126,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4164,7 +4142,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4173,19 +4151,23 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4209,13 +4191,11 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4233,28 +4213,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4262,21 +4242,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4288,17 +4268,15 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4335,31 +4313,31 @@
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
@@ -4376,21 +4354,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4399,23 +4377,21 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4424,7 +4400,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -4451,40 +4427,40 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4492,10 +4468,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4503,7 +4479,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -4518,18 +4494,20 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4577,7 +4555,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4595,10 +4573,10 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4606,10 +4584,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4632,18 +4610,18 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4691,7 +4669,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4709,10 +4687,10 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4720,10 +4698,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4746,17 +4724,17 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4805,7 +4783,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4823,10 +4801,10 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4834,10 +4812,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4860,19 +4838,17 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4921,7 +4897,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4939,10 +4915,10 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -4950,14 +4926,12 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4966,7 +4940,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -4978,19 +4952,19 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>209</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>213</v>
+        <v>269</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5015,11 +4989,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5037,13 +5013,13 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
@@ -5055,10 +5031,10 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>217</v>
+        <v>271</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5069,7 +5045,7 @@
         <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5089,19 +5065,23 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>180</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5149,7 +5129,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>183</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5161,16 +5141,16 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>184</v>
+        <v>280</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5178,21 +5158,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5201,20 +5181,18 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>135</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5239,52 +5217,52 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>187</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5292,10 +5270,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5303,10 +5281,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5318,20 +5296,16 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5355,13 +5329,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5379,13 +5353,13 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>232</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -5397,10 +5371,10 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5408,10 +5382,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5419,7 +5393,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -5428,23 +5402,21 @@
         <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>237</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5454,7 +5426,7 @@
         <v>77</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>77</v>
@@ -5469,13 +5441,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>294</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5493,10 +5465,10 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>88</v>
@@ -5511,10 +5483,10 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5522,10 +5494,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>244</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5536,7 +5508,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5548,18 +5520,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>246</v>
+        <v>299</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5583,13 +5553,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>77</v>
+        <v>300</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5607,13 +5577,13 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
@@ -5625,10 +5595,10 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5636,10 +5606,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>252</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5647,7 +5617,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -5659,21 +5629,19 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>253</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>254</v>
+        <v>305</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>255</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5721,13 +5689,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -5736,13 +5704,13 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5750,10 +5718,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5773,23 +5741,19 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5837,7 +5801,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5849,16 +5813,16 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>268</v>
+        <v>184</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5866,21 +5830,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -5889,23 +5853,21 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>281</v>
+        <v>135</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>282</v>
+        <v>186</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -5953,28 +5915,28 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>287</v>
+        <v>184</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -5982,42 +5944,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>289</v>
+        <v>190</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6041,13 +6007,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6065,28 +6031,28 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6094,10 +6060,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6105,10 +6071,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6117,16 +6083,16 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>194</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6156,10 +6122,10 @@
         <v>197</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>198</v>
+        <v>315</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>199</v>
+        <v>316</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6177,13 +6143,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -6195,10 +6161,10 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6206,10 +6172,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6226,19 +6192,19 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6250,7 +6216,7 @@
         <v>77</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>77</v>
@@ -6265,13 +6231,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6289,7 +6255,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>88</v>
@@ -6307,21 +6273,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6332,25 +6298,25 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6377,13 +6343,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6401,13 +6367,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6419,10 +6385,10 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>131</v>
+        <v>328</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6430,10 +6396,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6441,7 +6407,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -6456,13 +6422,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6513,13 +6479,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6528,13 +6494,13 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6542,10 +6508,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6565,18 +6531,20 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>181</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6625,7 +6593,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>183</v>
+        <v>334</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6637,16 +6605,16 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>184</v>
+        <v>340</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6654,21 +6622,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6680,16 +6648,16 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>335</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>135</v>
+        <v>342</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>186</v>
+        <v>343</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>137</v>
+        <v>338</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6727,87 +6695,85 @@
         <v>77</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>187</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>184</v>
+        <v>346</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>349</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>190</v>
+        <v>342</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>191</v>
+        <v>343</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -6855,28 +6821,28 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>192</v>
+        <v>341</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>131</v>
+        <v>346</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -6884,10 +6850,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6895,10 +6861,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -6910,13 +6876,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>194</v>
+        <v>351</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6943,13 +6909,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>322</v>
+        <v>77</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -6967,13 +6933,13 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
@@ -6985,10 +6951,10 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -6996,10 +6962,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7007,10 +6973,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7022,13 +6988,13 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>161</v>
+        <v>357</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7079,13 +7045,13 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7094,810 +7060,20 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AC53" s="2"/>
-      <c r="AD53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AN56" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN56">
+  <autoFilter ref="A1:AN49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7907,7 +7083,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
